--- a/Result/profitability/3036.xlsx
+++ b/Result/profitability/3036.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.88</v>
       </c>
       <c r="M2" t="n">
-        <v>2.855</v>
+        <v>3.4975</v>
       </c>
       <c r="N2" t="n">
-        <v>4.2925</v>
+        <v>4.195</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.8</v>
       </c>
       <c r="M3" t="n">
-        <v>2.6375</v>
+        <v>3.30625</v>
       </c>
       <c r="N3" t="n">
-        <v>4.58</v>
+        <v>4.491250000000001</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.67</v>
       </c>
       <c r="M4" t="n">
-        <v>2.43</v>
+        <v>3.0875</v>
       </c>
       <c r="N4" t="n">
-        <v>4.8775</v>
+        <v>4.73125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.98</v>
       </c>
       <c r="M5" t="n">
-        <v>2.005</v>
+        <v>2.68</v>
       </c>
       <c r="N5" t="n">
-        <v>4.965</v>
+        <v>4.85125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.4</v>
       </c>
       <c r="M6" t="n">
-        <v>1.77</v>
+        <v>2.305</v>
       </c>
       <c r="N6" t="n">
-        <v>5.065</v>
+        <v>5.02375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.45</v>
       </c>
       <c r="M7" t="n">
-        <v>1.40125</v>
+        <v>1.9025</v>
       </c>
       <c r="N7" t="n">
-        <v>5.211250000000001</v>
+        <v>5.170000000000001</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.75</v>
       </c>
       <c r="M8" t="n">
-        <v>1.03625</v>
+        <v>1.33125</v>
       </c>
       <c r="N8" t="n">
-        <v>5.3725</v>
+        <v>5.367500000000001</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3036</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>590694</v>
+      </c>
+      <c r="D75" t="n">
+        <v>570551</v>
+      </c>
+      <c r="E75" t="n">
+        <v>20142</v>
+      </c>
+      <c r="F75" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="G75" t="n">
+        <v>12994</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2.20%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-766</v>
+      </c>
+      <c r="J75" t="n">
+        <v>12227</v>
+      </c>
+      <c r="K75" t="n">
+        <v>9713</v>
+      </c>
+      <c r="L75" t="n">
+        <v>7.68</v>
+      </c>
+      <c r="M75" t="n">
+        <v>3.705</v>
+      </c>
+      <c r="N75" t="n">
+        <v>3.94375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>2.359999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.4436090225563909</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.04000000000000004</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.01159420289855073</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>2.368421052631579</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.9100000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.2106481481481481</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
